--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:04</t>
+    <t xml:space="preserve">2026-09-09 21:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:11</t>
+    <t xml:space="preserve">2026-09-18 09:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:03</t>
+    <t xml:space="preserve">2026-09-25 21:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -477,7 +477,7 @@
         <v>1242222.88</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>348684.57</v>
+        <v>348684.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:26</t>
+    <t xml:space="preserve">2026-10-05 02:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -596,7 +596,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1265521.12</v>
+        <v>1265521.13</v>
       </c>
     </row>
     <row r="5">
@@ -604,7 +604,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1260123.12</v>
+        <v>1260123.13</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1207088.62</v>
+        <v>1207088.63</v>
       </c>
     </row>
     <row r="7">
